--- a/data/inputs/Artikel & Materialien FGR+.XLSX
+++ b/data/inputs/Artikel & Materialien FGR+.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uklra\Downloads\ddmrp_mvp_monorepo\backend\data\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8105D042-DB35-4C61-8DC1-031FEE796F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C68ABF2-8110-4F98-B7B2-152C99CF12F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1084,7 +1084,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="2">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>

--- a/data/inputs/Artikel & Materialien FGR+.XLSX
+++ b/data/inputs/Artikel & Materialien FGR+.XLSX
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uklra\Downloads\ddmrp_mvp_monorepo\backend\data\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C68ABF2-8110-4F98-B7B2-152C99CF12F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBB156B-2F6B-4309-B0C5-CA79C97470AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -616,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="2">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
         <v>3</v>
@@ -642,7 +645,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -668,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -954,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -980,7 +983,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1006,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="2">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -1032,7 +1035,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -1058,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -1136,7 +1139,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -1188,7 +1191,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2">
         <v>3</v>
@@ -1240,7 +1243,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>3</v>
@@ -1266,7 +1269,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="2">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
@@ -1292,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="2">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -1318,7 +1321,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -1396,7 +1399,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="2">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
